--- a/Outputs/Scenarios/PtX_demand_HU_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HU_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002344042396197738</v>
       </c>
       <c r="K16" t="n">
-        <v>7.389742501572564e-05</v>
+        <v>0.0001724273250366932</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>7.389742501572568e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0001477948500314513</v>
+        <v>5.911794001258054e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1370,7 +1370,7 @@
         <v>0.001137068519571234</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0009684853274797893</v>
+        <v>0.0009684853274797894</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>3.377368313089167e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>2.463247500524188e-05</v>
+        <v>7.389742501572568e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.00347006938884947</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0003699816232180017</v>
+        <v>0.0008632904541753373</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3.699816232180018e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0007399632464360035</v>
+        <v>0.0002959852985744014</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001826352309920774</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0001233272077393339</v>
+        <v>3.699816232180018e-05</v>
       </c>
     </row>
     <row r="43">
